--- a/uploads/saturday schedule.xlsx
+++ b/uploads/saturday schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GitHub\nso_schedules\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1396C2A5-2E7D-4767-B84E-47A745012BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E665F9-1DCB-4E28-92DE-3CB26428EFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="202">
   <si>
     <t>Names</t>
   </si>
@@ -431,13 +431,240 @@
   </si>
   <si>
     <t>Joey</t>
+  </si>
+  <si>
+    <t>Kalob DeVries</t>
+  </si>
+  <si>
+    <t>Cassi DeVries</t>
+  </si>
+  <si>
+    <t>Set-up
+9:00 AM</t>
+  </si>
+  <si>
+    <t>WYST</t>
+  </si>
+  <si>
+    <t>Check-ins</t>
+  </si>
+  <si>
+    <t>Meet for PAT standup</t>
+  </si>
+  <si>
+    <t>Meet in Taylor Cultural Hall to talk about the day plan. Then help Rachel with check-in setup</t>
+  </si>
+  <si>
+    <t>Meet in Taylor Cultural Hall to talk about the day plan.</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 120</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 73</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 74</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 75</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 76</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 77</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 78</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 79</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 80</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 81</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 82</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 83</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 84</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 85</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 86</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 87</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 88</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 89</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 90</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 91</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 92</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 93</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 94</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 95</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 96</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 97</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 98</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 99</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 100</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 101</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 102</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 103</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 104</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 105</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 106</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 107</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 108</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 109</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 110</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 111</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 112</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 113</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 114</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 115</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 116</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 117</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 118</t>
+  </si>
+  <si>
+    <t>Be ready to go in Taylor 119</t>
+  </si>
+  <si>
+    <t>Pick up lunch
+11:15 PM</t>
+  </si>
+  <si>
+    <t>Pick up Little Caesars and Kainoa's with Kylie</t>
+  </si>
+  <si>
+    <t>Pick up Little Caesars and Kainoa's with Kalob</t>
+  </si>
+  <si>
+    <t>Clean up the courts and bring stuff back to the Biddulph. Count swag bags and pull out rix stix stuff</t>
+  </si>
+  <si>
+    <t>Go to transfer students (bring pennants)</t>
+  </si>
+  <si>
+    <t>Team is setting up</t>
+  </si>
+  <si>
+    <t>Tours</t>
+  </si>
+  <si>
+    <t>Kylie and kalob pick up lunch</t>
+  </si>
+  <si>
+    <t>Give Cassi a big, wet kiss</t>
+  </si>
+  <si>
+    <t>Kylie at parent orientation, Miriam at President's welcome, Talmage and Rachel at checkins</t>
+  </si>
+  <si>
+    <t>Mentor connections</t>
+  </si>
+  <si>
+    <t>Parent Info fair</t>
+  </si>
+  <si>
+    <t>kiss Kalob</t>
+  </si>
+  <si>
+    <t>Transition</t>
+  </si>
+  <si>
+    <t>Students attend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talmage and Rachel in I-center; Kylie, Tweedle dee, and tweedle dum at Taylor, Mirium at activity showcase. </t>
+  </si>
+  <si>
+    <t>Haha all the mentors at I-night</t>
+  </si>
+  <si>
+    <t>Treat cassi to something nice</t>
+  </si>
+  <si>
+    <t>You can help clean up or hang out with Cassi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,6 +683,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -836,15 +1069,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="14" max="14" width="11.7265625" customWidth="1"/>
+    <col min="2" max="3" width="16.54296875" customWidth="1"/>
+    <col min="16" max="16" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -852,2234 +1085,2323 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>85</v>
-      </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H2" t="s">
+        <v>89</v>
       </c>
       <c r="I2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" t="s">
         <v>103</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>115</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>118</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>85</v>
-      </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H3" t="s">
+        <v>89</v>
       </c>
       <c r="I3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" t="s">
         <v>103</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>115</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>118</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>85</v>
-      </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H4" t="s">
+        <v>89</v>
       </c>
       <c r="I4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" t="s">
         <v>103</v>
       </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>115</v>
       </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>118</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>89</v>
       </c>
       <c r="I5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K5" t="s">
         <v>103</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>115</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" t="s">
         <v>118</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H6" t="s">
+        <v>89</v>
       </c>
       <c r="I6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" t="s">
         <v>103</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>115</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P6" t="s">
         <v>118</v>
       </c>
-      <c r="P6" t="s">
+      <c r="R6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H7" t="s">
+        <v>89</v>
       </c>
       <c r="I7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" t="s">
         <v>103</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>115</v>
       </c>
-      <c r="N7" t="s">
+      <c r="P7" t="s">
         <v>118</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H8" t="s">
+        <v>89</v>
       </c>
       <c r="I8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" t="s">
         <v>103</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" t="s">
         <v>115</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
         <v>118</v>
       </c>
-      <c r="P8" t="s">
+      <c r="R8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H9" t="s">
+        <v>89</v>
       </c>
       <c r="I9" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" t="s">
         <v>103</v>
       </c>
-      <c r="M9" t="s">
+      <c r="O9" t="s">
         <v>115</v>
       </c>
-      <c r="N9" t="s">
+      <c r="P9" t="s">
         <v>118</v>
       </c>
-      <c r="P9" t="s">
+      <c r="R9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B10">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>89</v>
       </c>
       <c r="I10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" t="s">
         <v>103</v>
       </c>
-      <c r="M10" t="s">
+      <c r="O10" t="s">
         <v>115</v>
       </c>
-      <c r="N10" t="s">
+      <c r="P10" t="s">
         <v>118</v>
       </c>
-      <c r="P10" t="s">
+      <c r="R10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B11">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
       </c>
       <c r="I11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" t="s">
         <v>103</v>
       </c>
-      <c r="M11" t="s">
+      <c r="O11" t="s">
         <v>115</v>
       </c>
-      <c r="N11" t="s">
+      <c r="P11" t="s">
         <v>118</v>
       </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>89</v>
       </c>
       <c r="I12" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" t="s">
         <v>103</v>
       </c>
-      <c r="M12" t="s">
+      <c r="O12" t="s">
         <v>115</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>118</v>
       </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H13" t="s">
+        <v>89</v>
       </c>
       <c r="I13" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" t="s">
         <v>103</v>
       </c>
-      <c r="M13" t="s">
+      <c r="O13" t="s">
         <v>115</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
         <v>118</v>
       </c>
-      <c r="P13" t="s">
+      <c r="R13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B14">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H14" t="s">
+        <v>89</v>
       </c>
       <c r="I14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" t="s">
         <v>103</v>
       </c>
-      <c r="M14" t="s">
+      <c r="O14" t="s">
         <v>115</v>
       </c>
-      <c r="N14" t="s">
+      <c r="P14" t="s">
         <v>118</v>
       </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B15">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H15" t="s">
+        <v>89</v>
       </c>
       <c r="I15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K15" t="s">
         <v>103</v>
       </c>
-      <c r="M15" t="s">
+      <c r="O15" t="s">
         <v>115</v>
       </c>
-      <c r="N15" t="s">
+      <c r="P15" t="s">
         <v>118</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
       <c r="D16" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" t="s">
         <v>81</v>
       </c>
-      <c r="E16" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" t="s">
-        <v>89</v>
-      </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>89</v>
       </c>
       <c r="I16" t="s">
+        <v>99</v>
+      </c>
+      <c r="K16" t="s">
         <v>103</v>
       </c>
-      <c r="M16" t="s">
+      <c r="O16" t="s">
         <v>115</v>
       </c>
-      <c r="N16" t="s">
+      <c r="P16" t="s">
         <v>118</v>
       </c>
-      <c r="P16" t="s">
+      <c r="R16" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H17" t="s">
+        <v>89</v>
       </c>
       <c r="I17" t="s">
+        <v>99</v>
+      </c>
+      <c r="K17" t="s">
         <v>103</v>
       </c>
-      <c r="M17" t="s">
+      <c r="O17" t="s">
         <v>115</v>
       </c>
-      <c r="N17" t="s">
+      <c r="P17" t="s">
         <v>118</v>
       </c>
-      <c r="P17" t="s">
+      <c r="R17" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B18">
         <v>5</v>
       </c>
-      <c r="C18" t="s">
-        <v>85</v>
-      </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
+        <v>89</v>
       </c>
       <c r="I18" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" t="s">
         <v>103</v>
       </c>
-      <c r="M18" t="s">
+      <c r="O18" t="s">
         <v>115</v>
       </c>
-      <c r="N18" t="s">
+      <c r="P18" t="s">
         <v>118</v>
       </c>
-      <c r="P18" t="s">
+      <c r="R18" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B19">
         <v>14</v>
       </c>
-      <c r="C19" t="s">
-        <v>85</v>
-      </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H19" t="s">
+        <v>89</v>
       </c>
       <c r="I19" t="s">
+        <v>99</v>
+      </c>
+      <c r="K19" t="s">
         <v>103</v>
       </c>
-      <c r="M19" t="s">
+      <c r="O19" t="s">
         <v>115</v>
       </c>
-      <c r="N19" t="s">
+      <c r="P19" t="s">
         <v>118</v>
       </c>
-      <c r="P19" t="s">
+      <c r="R19" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B20">
         <v>14</v>
       </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H20" t="s">
+        <v>89</v>
       </c>
       <c r="I20" t="s">
+        <v>99</v>
+      </c>
+      <c r="K20" t="s">
         <v>103</v>
       </c>
-      <c r="M20" t="s">
+      <c r="O20" t="s">
         <v>115</v>
       </c>
-      <c r="N20" t="s">
+      <c r="P20" t="s">
         <v>118</v>
       </c>
-      <c r="P20" t="s">
+      <c r="R20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B21">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
-        <v>85</v>
-      </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H21" t="s">
+        <v>89</v>
       </c>
       <c r="I21" t="s">
+        <v>99</v>
+      </c>
+      <c r="K21" t="s">
         <v>103</v>
       </c>
-      <c r="M21" t="s">
+      <c r="O21" t="s">
         <v>115</v>
       </c>
-      <c r="N21" t="s">
+      <c r="P21" t="s">
         <v>118</v>
       </c>
-      <c r="P21" t="s">
+      <c r="R21" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B22">
         <v>17</v>
       </c>
-      <c r="C22" t="s">
-        <v>85</v>
-      </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H22" t="s">
+        <v>89</v>
       </c>
       <c r="I22" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" t="s">
         <v>103</v>
       </c>
-      <c r="M22" t="s">
+      <c r="O22" t="s">
         <v>115</v>
       </c>
-      <c r="N22" t="s">
+      <c r="P22" t="s">
         <v>118</v>
       </c>
-      <c r="P22" t="s">
+      <c r="R22" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B23">
         <v>8</v>
       </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
+        <v>89</v>
       </c>
       <c r="I23" t="s">
+        <v>99</v>
+      </c>
+      <c r="K23" t="s">
         <v>103</v>
       </c>
-      <c r="M23" t="s">
+      <c r="O23" t="s">
         <v>115</v>
       </c>
-      <c r="N23" t="s">
+      <c r="P23" t="s">
         <v>118</v>
       </c>
-      <c r="P23" t="s">
+      <c r="R23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B24">
         <v>7</v>
       </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H24" t="s">
+        <v>89</v>
       </c>
       <c r="I24" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" t="s">
         <v>103</v>
       </c>
-      <c r="M24" t="s">
+      <c r="O24" t="s">
         <v>115</v>
       </c>
-      <c r="N24" t="s">
+      <c r="P24" t="s">
         <v>118</v>
       </c>
-      <c r="P24" t="s">
+      <c r="R24" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B25">
         <v>7</v>
       </c>
-      <c r="C25" t="s">
-        <v>85</v>
-      </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H25" t="s">
+        <v>89</v>
       </c>
       <c r="I25" t="s">
+        <v>99</v>
+      </c>
+      <c r="K25" t="s">
         <v>103</v>
       </c>
-      <c r="M25" t="s">
+      <c r="O25" t="s">
         <v>115</v>
       </c>
-      <c r="N25" t="s">
+      <c r="P25" t="s">
         <v>118</v>
       </c>
-      <c r="P25" t="s">
+      <c r="R25" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B26">
         <v>12</v>
       </c>
-      <c r="C26" t="s">
-        <v>85</v>
-      </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H26" t="s">
+        <v>89</v>
       </c>
       <c r="I26" t="s">
+        <v>99</v>
+      </c>
+      <c r="K26" t="s">
         <v>103</v>
       </c>
-      <c r="M26" t="s">
+      <c r="O26" t="s">
         <v>115</v>
       </c>
-      <c r="N26" t="s">
+      <c r="P26" t="s">
         <v>118</v>
       </c>
-      <c r="P26" t="s">
+      <c r="R26" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B27">
         <v>12</v>
       </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="E27" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H27" t="s">
+        <v>89</v>
       </c>
       <c r="I27" t="s">
+        <v>99</v>
+      </c>
+      <c r="K27" t="s">
         <v>103</v>
       </c>
-      <c r="M27" t="s">
+      <c r="O27" t="s">
         <v>115</v>
       </c>
-      <c r="N27" t="s">
+      <c r="P27" t="s">
         <v>118</v>
       </c>
-      <c r="P27" t="s">
+      <c r="R27" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B28">
         <v>9</v>
       </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H28" t="s">
+        <v>89</v>
       </c>
       <c r="I28" t="s">
+        <v>99</v>
+      </c>
+      <c r="K28" t="s">
         <v>103</v>
       </c>
-      <c r="M28" t="s">
+      <c r="O28" t="s">
         <v>115</v>
       </c>
-      <c r="N28" t="s">
+      <c r="P28" t="s">
         <v>118</v>
       </c>
-      <c r="P28" t="s">
+      <c r="R28" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B29">
         <v>18</v>
       </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H29" t="s">
+        <v>89</v>
       </c>
       <c r="I29" t="s">
+        <v>99</v>
+      </c>
+      <c r="K29" t="s">
         <v>103</v>
       </c>
-      <c r="M29" t="s">
+      <c r="O29" t="s">
         <v>115</v>
       </c>
-      <c r="N29" t="s">
+      <c r="P29" t="s">
         <v>118</v>
       </c>
-      <c r="P29" t="s">
+      <c r="R29" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B30">
         <v>11</v>
       </c>
-      <c r="C30" t="s">
-        <v>85</v>
-      </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="E30" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H30" t="s">
+        <v>89</v>
       </c>
       <c r="I30" t="s">
+        <v>99</v>
+      </c>
+      <c r="K30" t="s">
         <v>103</v>
       </c>
-      <c r="M30" t="s">
+      <c r="O30" t="s">
         <v>115</v>
       </c>
-      <c r="N30" t="s">
+      <c r="P30" t="s">
         <v>118</v>
       </c>
-      <c r="P30" t="s">
+      <c r="R30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B31">
         <v>11</v>
       </c>
-      <c r="C31" t="s">
-        <v>85</v>
-      </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="E31" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H31" t="s">
+        <v>89</v>
       </c>
       <c r="I31" t="s">
+        <v>99</v>
+      </c>
+      <c r="K31" t="s">
         <v>103</v>
       </c>
-      <c r="M31" t="s">
+      <c r="O31" t="s">
         <v>115</v>
       </c>
-      <c r="N31" t="s">
+      <c r="P31" t="s">
         <v>118</v>
       </c>
-      <c r="P31" t="s">
+      <c r="R31" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B32">
         <v>10</v>
       </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G32" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H32" t="s">
+        <v>89</v>
       </c>
       <c r="I32" t="s">
+        <v>99</v>
+      </c>
+      <c r="K32" t="s">
         <v>103</v>
       </c>
-      <c r="M32" t="s">
+      <c r="O32" t="s">
         <v>115</v>
       </c>
-      <c r="N32" t="s">
+      <c r="P32" t="s">
         <v>118</v>
       </c>
-      <c r="P32" t="s">
+      <c r="R32" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>85</v>
-      </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="E33" t="s">
-        <v>73</v>
-      </c>
-      <c r="F33" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33" t="s">
         <v>92</v>
       </c>
-      <c r="G33" t="s">
-        <v>99</v>
-      </c>
-      <c r="O33" t="s">
+      <c r="I33" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q33" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>85</v>
-      </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" t="s">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" t="s">
         <v>92</v>
       </c>
-      <c r="G34" t="s">
-        <v>99</v>
-      </c>
-      <c r="O34" t="s">
+      <c r="I34" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q34" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>85</v>
-      </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="E35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F35" t="s">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" t="s">
         <v>92</v>
       </c>
-      <c r="G35" t="s">
-        <v>99</v>
-      </c>
-      <c r="O35" t="s">
+      <c r="I35" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q35" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>85</v>
-      </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" t="s">
         <v>92</v>
       </c>
-      <c r="G36" t="s">
-        <v>99</v>
-      </c>
-      <c r="O36" t="s">
+      <c r="I36" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q36" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C37" t="s">
-        <v>85</v>
-      </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" t="s">
+        <v>73</v>
+      </c>
+      <c r="H37" t="s">
         <v>92</v>
       </c>
-      <c r="G37" t="s">
-        <v>99</v>
-      </c>
-      <c r="O37" t="s">
+      <c r="I37" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q37" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C38" t="s">
-        <v>85</v>
-      </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F38" t="s">
+        <v>74</v>
+      </c>
+      <c r="G38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H38" t="s">
         <v>95</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
         <v>101</v>
       </c>
-      <c r="J38" t="s">
+      <c r="L38" t="s">
         <v>107</v>
       </c>
-      <c r="K38" t="s">
+      <c r="M38" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C39" t="s">
-        <v>85</v>
-      </c>
       <c r="D39" t="s">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
-        <v>73</v>
-      </c>
-      <c r="F39" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G39" t="s">
-        <v>99</v>
-      </c>
-      <c r="O39" t="s">
+        <v>73</v>
+      </c>
+      <c r="H39" t="s">
+        <v>89</v>
+      </c>
+      <c r="I39" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q39" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C40" t="s">
-        <v>85</v>
-      </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="E40" t="s">
-        <v>73</v>
-      </c>
-      <c r="F40" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G40" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H40" t="s">
+        <v>89</v>
       </c>
       <c r="I40" t="s">
+        <v>99</v>
+      </c>
+      <c r="K40" t="s">
         <v>104</v>
       </c>
-      <c r="M40" t="s">
+      <c r="O40" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="E41" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H41" t="s">
+        <v>89</v>
       </c>
       <c r="I41" t="s">
+        <v>99</v>
+      </c>
+      <c r="K41" t="s">
         <v>104</v>
       </c>
-      <c r="M41" t="s">
+      <c r="O41" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C42" t="s">
-        <v>85</v>
-      </c>
       <c r="D42" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="E42" t="s">
-        <v>73</v>
-      </c>
-      <c r="F42" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G42" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="H42" t="s">
+        <v>89</v>
       </c>
       <c r="I42" t="s">
+        <v>99</v>
+      </c>
+      <c r="K42" t="s">
         <v>104</v>
       </c>
-      <c r="M42" t="s">
+      <c r="O42" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C43" t="s">
-        <v>85</v>
-      </c>
       <c r="D43" t="s">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="E43" t="s">
-        <v>73</v>
-      </c>
-      <c r="F43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43" t="s">
+        <v>73</v>
+      </c>
+      <c r="H43" t="s">
         <v>95</v>
       </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
         <v>101</v>
       </c>
-      <c r="J43" t="s">
+      <c r="L43" t="s">
         <v>107</v>
       </c>
-      <c r="K43" t="s">
+      <c r="M43" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C44" t="s">
-        <v>85</v>
-      </c>
       <c r="D44" t="s">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="E44" t="s">
-        <v>73</v>
-      </c>
-      <c r="F44" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G44" t="s">
-        <v>99</v>
-      </c>
-      <c r="O44" t="s">
+        <v>73</v>
+      </c>
+      <c r="H44" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q44" t="s">
         <v>120</v>
       </c>
-      <c r="P44" t="s">
+      <c r="R44" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C45" t="s">
-        <v>85</v>
-      </c>
       <c r="D45" t="s">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="E45" t="s">
-        <v>73</v>
-      </c>
-      <c r="F45" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G45" t="s">
-        <v>99</v>
-      </c>
-      <c r="O45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H45" t="s">
+        <v>89</v>
+      </c>
+      <c r="I45" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q45" t="s">
         <v>120</v>
       </c>
-      <c r="P45" t="s">
+      <c r="R45" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C46" t="s">
-        <v>85</v>
-      </c>
       <c r="D46" t="s">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="E46" t="s">
-        <v>73</v>
-      </c>
-      <c r="F46" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G46" t="s">
-        <v>99</v>
-      </c>
-      <c r="O46" t="s">
+        <v>73</v>
+      </c>
+      <c r="H46" t="s">
+        <v>89</v>
+      </c>
+      <c r="I46" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q46" t="s">
         <v>120</v>
       </c>
-      <c r="P46" t="s">
+      <c r="R46" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C47" t="s">
-        <v>85</v>
-      </c>
       <c r="D47" t="s">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
-      </c>
-      <c r="F47" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G47" t="s">
-        <v>99</v>
-      </c>
-      <c r="O47" t="s">
+        <v>73</v>
+      </c>
+      <c r="H47" t="s">
+        <v>89</v>
+      </c>
+      <c r="I47" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q47" t="s">
         <v>120</v>
       </c>
-      <c r="P47" t="s">
+      <c r="R47" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C48" t="s">
-        <v>85</v>
-      </c>
       <c r="D48" t="s">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="E48" t="s">
-        <v>73</v>
-      </c>
-      <c r="F48" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G48" t="s">
-        <v>99</v>
-      </c>
-      <c r="O48" t="s">
+        <v>73</v>
+      </c>
+      <c r="H48" t="s">
+        <v>89</v>
+      </c>
+      <c r="I48" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q48" t="s">
         <v>120</v>
       </c>
-      <c r="P48" t="s">
+      <c r="R48" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C49" t="s">
-        <v>85</v>
-      </c>
       <c r="D49" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
-      </c>
-      <c r="F49" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G49" t="s">
-        <v>99</v>
-      </c>
-      <c r="O49" t="s">
+        <v>73</v>
+      </c>
+      <c r="H49" t="s">
+        <v>89</v>
+      </c>
+      <c r="I49" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q49" t="s">
         <v>120</v>
       </c>
-      <c r="P49" t="s">
+      <c r="R49" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C50" t="s">
-        <v>85</v>
-      </c>
       <c r="D50" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E50" t="s">
-        <v>73</v>
-      </c>
-      <c r="F50" t="s">
+        <v>74</v>
+      </c>
+      <c r="G50" t="s">
+        <v>73</v>
+      </c>
+      <c r="H50" t="s">
         <v>90</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>101</v>
       </c>
-      <c r="J50" t="s">
+      <c r="L50" t="s">
         <v>106</v>
       </c>
-      <c r="K50" t="s">
+      <c r="M50" t="s">
         <v>111</v>
       </c>
-      <c r="L50" t="s">
+      <c r="N50" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C51" t="s">
-        <v>85</v>
-      </c>
       <c r="D51" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E51" t="s">
-        <v>73</v>
-      </c>
-      <c r="F51" t="s">
+        <v>74</v>
+      </c>
+      <c r="G51" t="s">
+        <v>73</v>
+      </c>
+      <c r="H51" t="s">
         <v>90</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>101</v>
       </c>
-      <c r="J51" t="s">
+      <c r="L51" t="s">
         <v>106</v>
       </c>
-      <c r="K51" t="s">
+      <c r="M51" t="s">
         <v>111</v>
       </c>
-      <c r="L51" t="s">
+      <c r="N51" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C52" t="s">
-        <v>85</v>
-      </c>
       <c r="D52" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E52" t="s">
-        <v>73</v>
-      </c>
-      <c r="F52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G52" t="s">
+        <v>73</v>
+      </c>
+      <c r="H52" t="s">
         <v>90</v>
       </c>
-      <c r="H52" t="s">
+      <c r="J52" t="s">
         <v>101</v>
       </c>
-      <c r="J52" t="s">
+      <c r="L52" t="s">
         <v>106</v>
       </c>
-      <c r="K52" t="s">
+      <c r="M52" t="s">
         <v>111</v>
       </c>
-      <c r="L52" t="s">
+      <c r="N52" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C53" t="s">
-        <v>85</v>
-      </c>
       <c r="D53" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E53" t="s">
-        <v>73</v>
-      </c>
-      <c r="F53" t="s">
+        <v>74</v>
+      </c>
+      <c r="G53" t="s">
+        <v>73</v>
+      </c>
+      <c r="H53" t="s">
         <v>90</v>
       </c>
-      <c r="H53" t="s">
+      <c r="J53" t="s">
         <v>101</v>
       </c>
-      <c r="J53" t="s">
+      <c r="L53" t="s">
         <v>106</v>
       </c>
-      <c r="K53" t="s">
+      <c r="M53" t="s">
         <v>111</v>
       </c>
-      <c r="L53" t="s">
+      <c r="N53" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C54" t="s">
-        <v>85</v>
-      </c>
       <c r="D54" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E54" t="s">
-        <v>73</v>
-      </c>
-      <c r="F54" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" t="s">
+        <v>73</v>
+      </c>
+      <c r="H54" t="s">
         <v>90</v>
       </c>
-      <c r="H54" t="s">
+      <c r="J54" t="s">
         <v>101</v>
       </c>
-      <c r="J54" t="s">
+      <c r="L54" t="s">
         <v>106</v>
       </c>
-      <c r="K54" t="s">
+      <c r="M54" t="s">
         <v>111</v>
       </c>
-      <c r="L54" t="s">
+      <c r="N54" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C55" t="s">
-        <v>85</v>
-      </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="E55" t="s">
-        <v>73</v>
-      </c>
-      <c r="F55" t="s">
+        <v>74</v>
+      </c>
+      <c r="G55" t="s">
+        <v>73</v>
+      </c>
+      <c r="H55" t="s">
         <v>92</v>
       </c>
-      <c r="G55" t="s">
+      <c r="I55" t="s">
         <v>125</v>
       </c>
-      <c r="O55" t="s">
+      <c r="Q55" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C56" t="s">
-        <v>85</v>
-      </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="E56" t="s">
-        <v>73</v>
-      </c>
-      <c r="F56" t="s">
+        <v>74</v>
+      </c>
+      <c r="G56" t="s">
+        <v>73</v>
+      </c>
+      <c r="H56" t="s">
         <v>92</v>
       </c>
-      <c r="G56" t="s">
+      <c r="I56" t="s">
         <v>125</v>
       </c>
-      <c r="O56" t="s">
+      <c r="Q56" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C57" t="s">
-        <v>85</v>
-      </c>
       <c r="D57" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="E57" t="s">
-        <v>73</v>
-      </c>
-      <c r="F57" t="s">
+        <v>74</v>
+      </c>
+      <c r="G57" t="s">
+        <v>73</v>
+      </c>
+      <c r="H57" t="s">
         <v>91</v>
       </c>
-      <c r="G57" t="s">
+      <c r="I57" t="s">
         <v>126</v>
       </c>
-      <c r="O57" t="s">
+      <c r="Q57" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C58" t="s">
-        <v>85</v>
-      </c>
       <c r="D58" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
-      </c>
-      <c r="F58" t="s">
+        <v>74</v>
+      </c>
+      <c r="G58" t="s">
+        <v>73</v>
+      </c>
+      <c r="H58" t="s">
         <v>92</v>
       </c>
-      <c r="G58" t="s">
+      <c r="I58" t="s">
         <v>125</v>
       </c>
-      <c r="O58" t="s">
+      <c r="Q58" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C59" t="s">
-        <v>85</v>
-      </c>
       <c r="D59" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="E59" t="s">
-        <v>73</v>
-      </c>
-      <c r="F59" t="s">
+        <v>74</v>
+      </c>
+      <c r="G59" t="s">
+        <v>73</v>
+      </c>
+      <c r="H59" t="s">
         <v>91</v>
       </c>
-      <c r="G59" t="s">
-        <v>99</v>
-      </c>
-      <c r="O59" t="s">
+      <c r="I59" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q59" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C60" t="s">
-        <v>85</v>
-      </c>
       <c r="D60" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E60" t="s">
-        <v>73</v>
-      </c>
-      <c r="F60" t="s">
+        <v>74</v>
+      </c>
+      <c r="G60" t="s">
+        <v>73</v>
+      </c>
+      <c r="H60" t="s">
         <v>92</v>
       </c>
-      <c r="G60" t="s">
+      <c r="I60" t="s">
         <v>125</v>
       </c>
-      <c r="O60" t="s">
+      <c r="Q60" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C61" t="s">
-        <v>85</v>
-      </c>
       <c r="D61" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E61" t="s">
-        <v>73</v>
-      </c>
-      <c r="F61" t="s">
+        <v>74</v>
+      </c>
+      <c r="G61" t="s">
+        <v>73</v>
+      </c>
+      <c r="H61" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C62" t="s">
-        <v>85</v>
-      </c>
       <c r="D62" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E62" t="s">
-        <v>73</v>
-      </c>
-      <c r="F62" t="s">
+        <v>74</v>
+      </c>
+      <c r="G62" t="s">
+        <v>73</v>
+      </c>
+      <c r="H62" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C63" t="s">
-        <v>85</v>
-      </c>
       <c r="D63" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E63" t="s">
-        <v>73</v>
-      </c>
-      <c r="F63" t="s">
+        <v>74</v>
+      </c>
+      <c r="G63" t="s">
+        <v>73</v>
+      </c>
+      <c r="H63" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C64" t="s">
-        <v>85</v>
-      </c>
       <c r="D64" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F64" t="s">
+        <v>74</v>
+      </c>
+      <c r="G64" t="s">
+        <v>73</v>
+      </c>
+      <c r="H64" t="s">
         <v>92</v>
       </c>
-      <c r="G64" t="s">
-        <v>99</v>
-      </c>
-      <c r="O64" t="s">
+      <c r="I64" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q64" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C65" t="s">
-        <v>85</v>
-      </c>
       <c r="D65" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F65" t="s">
+        <v>74</v>
+      </c>
+      <c r="G65" t="s">
+        <v>73</v>
+      </c>
+      <c r="H65" t="s">
         <v>92</v>
       </c>
-      <c r="G65" t="s">
+      <c r="I65" t="s">
         <v>125</v>
       </c>
-      <c r="O65" t="s">
+      <c r="Q65" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C66" t="s">
-        <v>85</v>
-      </c>
       <c r="D66" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E66" t="s">
-        <v>73</v>
-      </c>
-      <c r="F66" t="s">
+        <v>74</v>
+      </c>
+      <c r="G66" t="s">
+        <v>73</v>
+      </c>
+      <c r="H66" t="s">
         <v>92</v>
       </c>
-      <c r="G66" t="s">
-        <v>99</v>
-      </c>
-      <c r="O66" t="s">
+      <c r="I66" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q66" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C67" t="s">
-        <v>85</v>
-      </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E67" t="s">
-        <v>73</v>
-      </c>
-      <c r="F67" t="s">
+        <v>74</v>
+      </c>
+      <c r="G67" t="s">
+        <v>73</v>
+      </c>
+      <c r="H67" t="s">
         <v>92</v>
       </c>
-      <c r="G67" t="s">
-        <v>99</v>
-      </c>
-      <c r="O67" t="s">
+      <c r="I67" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q67" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C68" t="s">
-        <v>85</v>
-      </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>73</v>
-      </c>
-      <c r="F68" t="s">
+        <v>74</v>
+      </c>
+      <c r="G68" t="s">
+        <v>73</v>
+      </c>
+      <c r="H68" t="s">
         <v>92</v>
       </c>
-      <c r="G68" t="s">
-        <v>99</v>
-      </c>
-      <c r="O68" t="s">
+      <c r="I68" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q68" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C69" t="s">
-        <v>85</v>
-      </c>
       <c r="D69" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E69" t="s">
-        <v>73</v>
-      </c>
-      <c r="F69" t="s">
+        <v>74</v>
+      </c>
+      <c r="G69" t="s">
+        <v>73</v>
+      </c>
+      <c r="H69" t="s">
         <v>92</v>
       </c>
-      <c r="G69" t="s">
-        <v>99</v>
-      </c>
-      <c r="O69" t="s">
+      <c r="I69" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q69" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C70" t="s">
-        <v>85</v>
-      </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E70" t="s">
-        <v>73</v>
-      </c>
-      <c r="F70" t="s">
+        <v>74</v>
+      </c>
+      <c r="G70" t="s">
+        <v>73</v>
+      </c>
+      <c r="H70" t="s">
         <v>92</v>
       </c>
-      <c r="G70" t="s">
+      <c r="I70" t="s">
         <v>125</v>
       </c>
-      <c r="O70" t="s">
+      <c r="Q70" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C71" t="s">
-        <v>85</v>
-      </c>
       <c r="D71" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E71" t="s">
-        <v>73</v>
-      </c>
-      <c r="F71" t="s">
+        <v>74</v>
+      </c>
+      <c r="G71" t="s">
+        <v>73</v>
+      </c>
+      <c r="H71" t="s">
         <v>91</v>
       </c>
-      <c r="G71" t="s">
+      <c r="I71" t="s">
         <v>126</v>
       </c>
-      <c r="O71" t="s">
+      <c r="Q71" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C72" t="s">
-        <v>85</v>
-      </c>
       <c r="D72" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E72" t="s">
-        <v>73</v>
-      </c>
-      <c r="F72" t="s">
+        <v>74</v>
+      </c>
+      <c r="G72" t="s">
+        <v>73</v>
+      </c>
+      <c r="H72" t="s">
         <v>92</v>
       </c>
-      <c r="G72" t="s">
+      <c r="I72" t="s">
         <v>125</v>
       </c>
-      <c r="O72" t="s">
+      <c r="Q72" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C73" t="s">
+        <v>130</v>
+      </c>
+      <c r="D73" t="s">
         <v>85</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>80</v>
       </c>
-      <c r="E73" t="s">
-        <v>73</v>
-      </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
+        <v>73</v>
+      </c>
+      <c r="H73" t="s">
         <v>93</v>
       </c>
-      <c r="G73" t="s">
-        <v>99</v>
-      </c>
-      <c r="O73" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="I73" t="s">
+        <v>99</v>
+      </c>
+      <c r="K73" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C74" t="s">
+        <v>130</v>
+      </c>
+      <c r="D74" t="s">
         <v>85</v>
       </c>
-      <c r="D74" t="s">
-        <v>83</v>
-      </c>
       <c r="E74" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F74" t="s">
+        <v>185</v>
+      </c>
+      <c r="G74" t="s">
+        <v>73</v>
+      </c>
+      <c r="H74" t="s">
         <v>95</v>
       </c>
-      <c r="H74" t="s">
+      <c r="J74" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" s="11" t="s">
         <v>76</v>
       </c>
       <c r="C75" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="D75" t="s">
+        <v>132</v>
+      </c>
+      <c r="E75" t="s">
         <v>83</v>
       </c>
-      <c r="E75" t="s">
-        <v>73</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
+        <v>73</v>
+      </c>
+      <c r="H75" t="s">
         <v>97</v>
       </c>
-      <c r="G75" t="s">
-        <v>99</v>
-      </c>
-      <c r="O75" t="s">
+      <c r="I75" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q75" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" s="11" t="s">
         <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>85</v>
-      </c>
-      <c r="D76" t="s">
+        <v>94</v>
+      </c>
+      <c r="E76" t="s">
         <v>82</v>
       </c>
-      <c r="E76" t="s">
-        <v>73</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
+        <v>73</v>
+      </c>
+      <c r="H76" t="s">
         <v>94</v>
       </c>
-      <c r="G76" t="s">
-        <v>99</v>
-      </c>
-      <c r="O76" t="s">
+      <c r="I76" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q76" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>85</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>80</v>
       </c>
-      <c r="E77" t="s">
-        <v>73</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
+        <v>73</v>
+      </c>
+      <c r="H77" t="s">
         <v>93</v>
       </c>
-      <c r="G77" t="s">
-        <v>99</v>
-      </c>
-      <c r="O77" t="s">
+      <c r="I77" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q77" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>85</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>80</v>
       </c>
-      <c r="E78" t="s">
-        <v>73</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
+        <v>73</v>
+      </c>
+      <c r="H78" t="s">
         <v>93</v>
       </c>
-      <c r="G78" t="s">
-        <v>99</v>
-      </c>
-      <c r="O78" t="s">
+      <c r="I78" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q78" t="s">
         <v>121</v>
       </c>
     </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A79" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F79" t="s">
+        <v>184</v>
+      </c>
+      <c r="G79" t="s">
+        <v>73</v>
+      </c>
+      <c r="H79" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>201</v>
+      </c>
+      <c r="R79" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A80" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" t="s">
+        <v>188</v>
+      </c>
+      <c r="E80" t="s">
+        <v>189</v>
+      </c>
+      <c r="F80" t="s">
+        <v>190</v>
+      </c>
+      <c r="G80" t="s">
+        <v>73</v>
+      </c>
+      <c r="H80" t="s">
+        <v>192</v>
+      </c>
+      <c r="I80" t="s">
+        <v>99</v>
+      </c>
+      <c r="J80" t="s">
+        <v>101</v>
+      </c>
+      <c r="K80" t="s">
+        <v>193</v>
+      </c>
+      <c r="L80" t="s">
+        <v>194</v>
+      </c>
+      <c r="M80" t="s">
+        <v>195</v>
+      </c>
+      <c r="O80" t="s">
+        <v>196</v>
+      </c>
+      <c r="P80" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>198</v>
+      </c>
+      <c r="R80" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/uploads/saturday schedule.xlsx
+++ b/uploads/saturday schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GitHub\nso_schedules\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E665F9-1DCB-4E28-92DE-3CB26428EFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B788E6F1-F4EF-4A6A-BAB7-C7BF22F83C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="226">
   <si>
     <t>Names</t>
   </si>
@@ -658,6 +658,78 @@
   </si>
   <si>
     <t>You can help clean up or hang out with Cassi</t>
+  </si>
+  <si>
+    <t>Nate Watson</t>
+  </si>
+  <si>
+    <t>Stephanie Colvin</t>
+  </si>
+  <si>
+    <t>Ruth Lauti</t>
+  </si>
+  <si>
+    <t>Kimball Benson</t>
+  </si>
+  <si>
+    <t>Chris Gomm</t>
+  </si>
+  <si>
+    <t>Joey Bennett</t>
+  </si>
+  <si>
+    <t>Sam Brubaker</t>
+  </si>
+  <si>
+    <t>Taylor Foyer</t>
+  </si>
+  <si>
+    <t>Set up booth for Parent orientation</t>
+  </si>
+  <si>
+    <t>Parents arrive at Taylor building</t>
+  </si>
+  <si>
+    <t>Parents arrive te Taylor building</t>
+  </si>
+  <si>
+    <t>Say prayer during the session and clean up booth</t>
+  </si>
+  <si>
+    <t>Attend in the Hart Gym with the parents</t>
+  </si>
+  <si>
+    <t>Transition to the Hart Gym</t>
+  </si>
+  <si>
+    <t>Hart Gym</t>
+  </si>
+  <si>
+    <t>Go to Hart Gym for Transfer Students</t>
+  </si>
+  <si>
+    <t>Be ready for Parent orientation in the Taylor</t>
+  </si>
+  <si>
+    <t>I-Center</t>
+  </si>
+  <si>
+    <t>Students check in at I-center, Parents at the Taylor building</t>
+  </si>
+  <si>
+    <t>Students arrive at the I-Center</t>
+  </si>
+  <si>
+    <t>Lunch in Taylor Cultural Hall</t>
+  </si>
+  <si>
+    <t>Taylor Chapel</t>
+  </si>
+  <si>
+    <t>Transfer Students go to Hart Gym</t>
+  </si>
+  <si>
+    <t>Everyone moves to Hart Gym</t>
   </si>
 </sst>
 </file>
@@ -694,7 +766,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -749,6 +821,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -762,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -783,6 +861,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R80"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.1796875" customWidth="1"/>
@@ -3400,6 +3479,182 @@
         <v>199</v>
       </c>
     </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A81" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E81" t="s">
+        <v>209</v>
+      </c>
+      <c r="G81" t="s">
+        <v>222</v>
+      </c>
+      <c r="H81" t="s">
+        <v>217</v>
+      </c>
+      <c r="J81" t="s">
+        <v>211</v>
+      </c>
+      <c r="O81" t="s">
+        <v>225</v>
+      </c>
+      <c r="P81" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A82" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E82" t="s">
+        <v>209</v>
+      </c>
+      <c r="G82" t="s">
+        <v>222</v>
+      </c>
+      <c r="H82" t="s">
+        <v>217</v>
+      </c>
+      <c r="J82" t="s">
+        <v>212</v>
+      </c>
+      <c r="O82" t="s">
+        <v>225</v>
+      </c>
+      <c r="P82" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A83" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E83" t="s">
+        <v>209</v>
+      </c>
+      <c r="G83" t="s">
+        <v>222</v>
+      </c>
+      <c r="H83" t="s">
+        <v>210</v>
+      </c>
+      <c r="J83" t="s">
+        <v>211</v>
+      </c>
+      <c r="M83" t="s">
+        <v>213</v>
+      </c>
+      <c r="N83" t="s">
+        <v>215</v>
+      </c>
+      <c r="P83" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A84" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E84" t="s">
+        <v>209</v>
+      </c>
+      <c r="G84" t="s">
+        <v>222</v>
+      </c>
+      <c r="H84" t="s">
+        <v>218</v>
+      </c>
+      <c r="J84" t="s">
+        <v>211</v>
+      </c>
+      <c r="M84" t="s">
+        <v>223</v>
+      </c>
+      <c r="N84" t="s">
+        <v>215</v>
+      </c>
+      <c r="P84" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A85" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E85" t="s">
+        <v>209</v>
+      </c>
+      <c r="G85" t="s">
+        <v>222</v>
+      </c>
+      <c r="H85" t="s">
+        <v>219</v>
+      </c>
+      <c r="J85" t="s">
+        <v>211</v>
+      </c>
+      <c r="O85" t="s">
+        <v>225</v>
+      </c>
+      <c r="P85" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A86" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E86" t="s">
+        <v>209</v>
+      </c>
+      <c r="G86" t="s">
+        <v>222</v>
+      </c>
+      <c r="H86" t="s">
+        <v>219</v>
+      </c>
+      <c r="J86" t="s">
+        <v>211</v>
+      </c>
+      <c r="O86" t="s">
+        <v>225</v>
+      </c>
+      <c r="P86" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A87" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E87" t="s">
+        <v>209</v>
+      </c>
+      <c r="G87" t="s">
+        <v>222</v>
+      </c>
+      <c r="H87" t="s">
+        <v>220</v>
+      </c>
+      <c r="I87" t="s">
+        <v>221</v>
+      </c>
+      <c r="J87" t="s">
+        <v>211</v>
+      </c>
+      <c r="K87" t="s">
+        <v>224</v>
+      </c>
+      <c r="M87" t="s">
+        <v>223</v>
+      </c>
+      <c r="O87" t="s">
+        <v>225</v>
+      </c>
+      <c r="P87" t="s">
+        <v>216</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
